--- a/data/messages.xlsx
+++ b/data/messages.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_8E1D06664701C2F194C2120D8BEBEB3E4C10BF31" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83BC859-0B95-40D1-933D-7B4B5D465616}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616"/>
   </bookViews>
   <sheets>
-    <sheet name="Messages" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Messages" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -30,19 +29,34 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>HARISHRAJ C</t>
+  </si>
+  <si>
+    <t>HARISHCC2007@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>hlo</t>
+  </si>
+  <si>
+    <t>14/4/2026, 5:21:12 pm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -411,9 +425,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
@@ -438,13 +452,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/messages.xlsx
+++ b/data/messages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616"/>
+    <workbookView xWindow="3684" yWindow="4440" windowWidth="17280" windowHeight="9960"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Messages" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -44,6 +44,33 @@
   </si>
   <si>
     <t>14/4/2026, 5:21:12 pm</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>24/5/2026, 7:53:19 am</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>24/5/2026, 7:54:56 am</t>
+  </si>
+  <si>
+    <t>hari</t>
+  </si>
+  <si>
+    <t>harish@gmail.com</t>
+  </si>
+  <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>24/5/2026, 8:02:53 am</t>
+  </si>
+  <si>
+    <t>24/5/2026, 8:05:35 am</t>
   </si>
 </sst>
 </file>
@@ -426,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -452,21 +479,89 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/messages.xlsx
+++ b/data/messages.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>24/5/2026, 8:05:35 am</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>19/7/2026, 4:32:17 pm</t>
   </si>
 </sst>
 </file>
@@ -453,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -564,6 +570,23 @@
         <v>18</v>
       </c>
     </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
